--- a/public/internal_assessee.xlsx
+++ b/public/internal_assessee.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adisa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KPN Corp\KPN Assessment\kpn-assessment-fe\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C7F4D5C-A038-47A5-A529-E9C9C1A31219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BD2C12-DD6B-4B30-A1A3-DA5634804A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{C9815A66-2956-44CE-A8C1-F61D00F13D0E}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="7368" xr2:uid="{C9815A66-2956-44CE-A8C1-F61D00F13D0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -93,18 +93,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -421,39 +418,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DE5CAC-BCA3-47AB-BCD4-FCA0D4857D3F}">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/public/internal_assessee.xlsx
+++ b/public/internal_assessee.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KPN Corp\KPN Assessment\kpn-assessment-fe\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BD2C12-DD6B-4B30-A1A3-DA5634804A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="7368" xr2:uid="{C9815A66-2956-44CE-A8C1-F61D00F13D0E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,18 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>assessee_nik</t>
-  </si>
-  <si>
-    <t>01122110013</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -417,22 +413,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8DE5CAC-BCA3-47AB-BCD4-FCA0D4857D3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
